--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner-role.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner-role.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -637,7 +637,7 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
@@ -975,7 +975,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0)
 </t>
   </si>
   <si>
@@ -991,7 +991,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1019,7 +1019,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1037,7 +1037,7 @@
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1052,7 +1052,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0)
 </t>
   </si>
   <si>
@@ -1093,7 +1093,7 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0-ballot-2}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1583,7 +1583,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.7265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.1796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1598,7 +1598,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.93359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.38671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
